--- a/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -665,17 +665,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1045,15 +1045,15 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1332,20 +1332,20 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1403,9 +1403,9 @@
       <c r="I13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1476,9 +1476,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1547,24 +1547,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1619,10 +1619,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1631,39 +1629,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1697,7 +1693,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1731,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1764,17 +1760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1845,9 +1841,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1877,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1918,9 +1914,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1950,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1980,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1989,24 +1985,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2023,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2062,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2096,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2129,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2208,11 +2204,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2242,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2272,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2280,47 +2276,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2345,33 +2345,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2564,33 +2564,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2600,19 +2600,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2673,19 +2673,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2719,11 +2719,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2746,19 +2746,19 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2783,20 +2783,20 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2805,11 +2805,11 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2856,33 +2856,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2892,19 +2892,19 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2938,11 +2938,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3002,33 +3002,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3038,19 +3038,19 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3088,20 +3088,20 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3111,19 +3111,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3157,11 +3157,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3184,19 +3184,19 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3221,33 +3221,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3297,17 +3297,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,12 +3337,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3375,10 +3375,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3387,39 +3385,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3444,7 +3440,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3453,24 +3449,24 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3487,12 +3483,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3517,12 +3513,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -3530,20 +3526,20 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3560,12 +3556,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3590,7 +3586,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3598,51 +3594,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3676,7 +3668,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3710,12 +3702,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3740,7 +3732,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3749,24 +3741,24 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3783,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3813,7 +3805,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3821,10 +3813,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3833,39 +3823,37 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3890,7 +3878,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3898,51 +3886,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3970,9 +3954,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -4010,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4087,12 +4071,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4126,7 +4110,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4160,12 +4144,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4190,7 +4174,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4203,20 +4187,20 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4233,12 +4217,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4310,12 +4294,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4343,9 +4327,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
@@ -4383,12 +4367,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4422,11 +4406,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4456,12 +4440,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4486,7 +4470,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4494,8 +4478,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4504,37 +4490,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4559,7 +4547,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4567,47 +4555,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4635,17 +4627,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4675,12 +4667,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4705,7 +4697,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4713,47 +4705,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4787,7 +4783,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4821,12 +4817,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4851,7 +4847,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4860,24 +4856,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4894,12 +4890,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4924,7 +4920,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4932,8 +4928,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4942,37 +4940,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5000,9 +5000,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
@@ -5040,12 +5040,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5113,12 +5113,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5186,12 +5186,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5238,11 +5238,11 @@
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5438,17 +5438,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5517,11 +5517,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5592,9 +5592,9 @@
       <c r="I70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5654,33 +5654,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5736,11 +5736,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5809,11 +5809,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5843,12 +5843,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5882,24 +5882,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5949,17 +5949,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5989,12 +5989,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6028,11 +6028,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6101,11 +6101,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6165,33 +6165,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6311,29 +6311,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
+          <t>R$ 60,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,8%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,9%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -6354,12 +6354,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6393,24 +6393,24 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6466,11 +6466,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6500,12 +6500,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6530,33 +6530,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 269,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,7%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6573,12 +6573,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6612,11 +6612,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6685,11 +6685,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6749,33 +6749,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6825,22 +6825,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>3</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6865,12 +6865,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6904,11 +6904,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6968,33 +6968,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 209,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,8%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5000,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7050,24 +7050,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7122,51 +7122,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7191,33 +7187,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 269,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,7%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>27</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7234,12 +7230,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7267,17 +7263,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7307,12 +7303,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7337,7 +7333,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7345,10 +7341,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7357,39 +7351,37 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7414,33 +7406,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7457,12 +7449,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7487,33 +7479,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7530,12 +7522,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7560,7 +7552,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7568,10 +7560,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7580,39 +7570,37 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7637,7 +7625,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 209,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7646,24 +7634,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>51</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5000,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7680,12 +7668,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7710,7 +7698,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7718,51 +7706,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I99" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7787,7 +7771,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7795,8 +7779,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7805,37 +7791,39 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7863,17 +7851,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7903,12 +7891,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7933,7 +7921,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7941,51 +7929,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8010,7 +7994,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8018,47 +8002,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8083,33 +8071,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8126,12 +8114,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8165,7 +8153,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8199,12 +8187,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8229,7 +8217,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8237,8 +8225,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="n">
-        <v>1</v>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8247,37 +8237,39 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8302,33 +8294,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8345,12 +8337,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8375,55 +8367,59 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8459,9 +8455,9 @@
       <c r="I109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8491,12 +8487,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8521,33 +8517,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8564,12 +8560,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8594,7 +8590,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8602,8 +8598,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>3</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8612,37 +8610,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8676,11 +8676,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8743,30 +8743,30 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8856,82 +8856,739 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-PT</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada preto</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>4851133050</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O115"/>
+  <autoFilter ref="A1:O124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -675,20 +675,20 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1111,9 +1111,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1264,15 +1264,15 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1403,9 +1403,9 @@
       <c r="I13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2133,9 +2133,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -2213,15 +2213,15 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2276,10 +2276,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2288,41 +2286,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2354,11 +2350,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2388,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2427,11 +2423,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2491,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2499,8 +2495,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2509,39 +2507,41 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,14 +2607,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2646,11 +2646,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2680,14 +2680,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2721,9 +2721,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,14 +2753,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2786,17 +2786,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2867,9 +2867,9 @@
       <c r="I33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2899,14 +2899,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2938,11 +2938,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2972,14 +2972,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3002,33 +3002,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3045,14 +3045,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3084,11 +3084,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3118,14 +3118,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3157,11 +3157,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3191,14 +3191,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3221,20 +3221,20 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3243,11 +3243,11 @@
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3257,21 +3257,21 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3297,17 +3297,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3330,21 +3330,21 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3376,11 +3376,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3403,21 +3403,21 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3483,14 +3483,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3513,33 +3513,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3556,14 +3556,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3595,11 +3595,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,14 +3629,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3668,24 +3668,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3702,14 +3702,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3737,20 +3737,20 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3775,14 +3775,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3814,11 +3814,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,14 +3848,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3887,11 +3887,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3960,24 +3960,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3994,14 +3994,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4032,10 +4032,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4044,41 +4042,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4110,11 +4106,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4144,14 +4140,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4183,11 +4179,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4217,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4294,14 +4290,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4333,7 +4329,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4367,14 +4363,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4406,11 +4402,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4440,12 +4436,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4517,14 +4513,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4547,7 +4543,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4555,10 +4551,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4567,41 +4561,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4627,17 +4619,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4667,12 +4659,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4744,14 +4736,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4774,7 +4766,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4782,8 +4774,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4792,39 +4786,41 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4847,33 +4843,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4890,12 +4886,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4967,14 +4963,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5000,9 +4996,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
@@ -5040,14 +5036,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5070,7 +5066,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5079,24 +5075,24 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5113,14 +5109,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5143,7 +5139,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5151,8 +5147,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5161,39 +5159,41 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5216,20 +5216,20 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5238,11 +5238,11 @@
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5259,14 +5259,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5298,11 +5298,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5332,14 +5332,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5373,9 +5373,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -5405,14 +5405,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5444,24 +5444,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5478,14 +5478,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5517,11 +5517,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5551,14 +5551,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5590,11 +5590,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5624,14 +5624,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5697,14 +5697,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5770,14 +5770,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5843,14 +5843,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5884,9 +5884,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5916,14 +5916,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5957,9 +5957,9 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5989,14 +5989,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6030,9 +6030,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6062,14 +6062,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6095,17 +6095,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6135,14 +6135,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6174,11 +6174,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6208,14 +6208,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6247,11 +6247,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6281,14 +6281,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6311,33 +6311,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6354,14 +6354,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6393,11 +6393,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6427,14 +6427,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6466,11 +6466,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6500,14 +6500,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6530,33 +6530,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 60,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6573,14 +6573,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6606,17 +6606,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6646,14 +6646,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6685,11 +6685,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6719,14 +6719,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6749,33 +6749,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6792,14 +6792,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6822,33 +6822,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6865,14 +6865,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6904,11 +6904,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6938,14 +6938,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6968,33 +6968,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7011,14 +7011,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7046,20 +7046,20 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7084,14 +7084,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7123,11 +7123,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7157,14 +7157,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7187,20 +7187,20 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 269,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,7%</t>
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,8%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7209,11 +7209,11 @@
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7230,14 +7230,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7260,33 +7260,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7376,14 +7376,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7406,33 +7406,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
+          <t>R$ 269,00</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,7%</t>
+          <t>▲ 21,7%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,6%</t>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7449,14 +7449,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7479,33 +7479,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>5</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7522,14 +7522,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7595,14 +7595,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7625,33 +7625,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 209,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5000,0%</t>
+        <v>42</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7668,14 +7668,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7698,33 +7698,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7741,14 +7741,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7779,10 +7779,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7791,41 +7789,39 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7848,7 +7844,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 209,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7857,24 +7853,24 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>51</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5000,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7891,14 +7887,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7921,7 +7917,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7930,24 +7926,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7964,12 +7960,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8041,14 +8037,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8080,11 +8076,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8114,14 +8110,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8153,11 +8149,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8187,12 +8183,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8264,14 +8260,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8303,11 +8299,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8337,14 +8333,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8367,7 +8363,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8375,10 +8371,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8387,41 +8381,39 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8444,7 +8436,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8452,8 +8444,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8462,39 +8456,41 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8520,17 +8516,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8560,12 +8556,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8637,14 +8633,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8678,9 +8674,9 @@
       <c r="I112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8710,14 +8706,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8740,33 +8736,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8783,14 +8779,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8813,7 +8809,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8821,8 +8817,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
-        <v>0</v>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -8831,39 +8829,41 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8895,11 +8895,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
@@ -8929,14 +8929,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8959,25 +8959,25 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9002,14 +9002,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9035,17 +9035,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9075,14 +9075,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9114,11 +9114,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
@@ -9148,14 +9148,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9181,17 +9181,17 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9221,14 +9221,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9251,33 +9251,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9294,14 +9294,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9333,11 +9333,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9367,14 +9367,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9397,33 +9397,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9440,14 +9440,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9488,15 +9488,15 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9513,82 +9513,301 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-PT</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada preto</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4851133050</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O124" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O124"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -698,19 +698,19 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -771,19 +771,19 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -813,20 +813,20 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -844,19 +844,19 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -917,19 +917,19 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -990,19 +990,19 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -1040,20 +1040,20 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1063,19 +1063,19 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1136,19 +1136,19 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1209,19 +1209,19 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1921,15 +1921,15 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1979,17 +1979,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -2208,20 +2208,20 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2279,9 +2279,9 @@
       <c r="I25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2352,9 +2352,9 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2423,24 +2423,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2495,10 +2495,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2507,39 +2505,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2573,7 +2569,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2607,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2640,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2680,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2721,9 +2717,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2794,9 +2790,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2826,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2856,7 +2852,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2865,24 +2861,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2899,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2938,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2972,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3005,17 +3001,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3084,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3118,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3148,7 +3144,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3156,47 +3152,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3221,33 +3221,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,12 +3337,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3376,11 +3376,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3440,33 +3440,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3476,19 +3476,19 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3516,17 +3516,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3549,19 +3549,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3595,11 +3595,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3622,19 +3622,19 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3659,20 +3659,20 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3681,11 +3681,11 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3695,19 +3695,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3732,33 +3732,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3768,19 +3768,19 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3814,11 +3814,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3841,19 +3841,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3878,33 +3878,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3914,19 +3914,19 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3964,20 +3964,20 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3987,19 +3987,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4033,11 +4033,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4060,19 +4060,19 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4097,33 +4097,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4173,17 +4173,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4251,10 +4251,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4263,39 +4261,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4320,7 +4316,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4329,24 +4325,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4363,12 +4359,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4393,12 +4389,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -4406,20 +4402,20 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4436,12 +4432,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4466,7 +4462,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4474,51 +4470,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4552,7 +4544,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4586,12 +4578,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4616,7 +4608,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4625,24 +4617,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4659,12 +4651,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4689,7 +4681,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4697,10 +4689,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4709,39 +4699,37 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4766,7 +4754,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4774,51 +4762,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4846,9 +4830,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -4886,12 +4870,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4963,12 +4947,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5002,7 +4986,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5036,12 +5020,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5066,7 +5050,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5079,20 +5063,20 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5109,12 +5093,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5186,12 +5170,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5219,9 +5203,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
@@ -5259,12 +5243,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5298,11 +5282,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5332,12 +5316,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5362,7 +5346,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5370,8 +5354,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5380,37 +5366,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5435,7 +5423,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5443,47 +5431,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5511,17 +5503,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5551,12 +5543,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5581,7 +5573,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5589,47 +5581,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5663,7 +5659,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5697,12 +5693,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5727,7 +5723,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5736,24 +5732,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5770,12 +5766,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5800,7 +5796,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5808,8 +5804,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>1</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5818,37 +5816,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5876,9 +5876,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
@@ -5916,12 +5916,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -5989,12 +5989,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6114,11 +6114,11 @@
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6314,17 +6314,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6354,12 +6354,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6393,11 +6393,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6468,9 +6468,9 @@
       <c r="I82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6500,12 +6500,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6530,33 +6530,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6573,12 +6573,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6612,11 +6612,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6685,11 +6685,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6758,24 +6758,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6825,17 +6825,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6865,12 +6865,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6904,11 +6904,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6977,11 +6977,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7041,33 +7041,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7187,29 +7187,29 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
+          <t>R$ 60,00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,8%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,9%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -7230,12 +7230,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7269,24 +7269,24 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7342,11 +7342,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7376,12 +7376,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7406,33 +7406,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 269,00</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,7%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7488,11 +7488,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7561,11 +7561,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7625,33 +7625,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7668,12 +7668,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7701,22 +7701,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>3</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7780,11 +7780,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7814,12 +7814,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7844,33 +7844,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 209,00</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,8%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5000,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7887,12 +7887,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7926,24 +7926,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -7998,51 +7998,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8067,33 +8063,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 269,00</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,7%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>27</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8110,12 +8106,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8143,17 +8139,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8183,12 +8179,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8213,7 +8209,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8221,10 +8217,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8233,39 +8227,37 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8290,33 +8282,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8333,12 +8325,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8363,33 +8355,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8406,12 +8398,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8436,7 +8428,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8444,10 +8436,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8456,39 +8446,37 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8513,7 +8501,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 209,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8522,24 +8510,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>51</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5000,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8556,12 +8544,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8586,7 +8574,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8594,51 +8582,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I111" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8663,7 +8647,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8671,8 +8655,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n">
-        <v>0</v>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8681,37 +8667,39 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8739,17 +8727,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8779,12 +8767,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8809,7 +8797,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8817,51 +8805,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8886,7 +8870,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8894,47 +8878,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8959,33 +8947,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9002,12 +8990,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9041,7 +9029,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9075,12 +9063,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9105,7 +9093,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9113,8 +9101,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="n">
-        <v>1</v>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9123,37 +9113,39 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9178,33 +9170,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9221,12 +9213,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9251,55 +9243,59 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9335,9 +9331,9 @@
       <c r="I121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9367,12 +9363,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9397,33 +9393,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9440,12 +9436,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9470,7 +9466,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9478,8 +9474,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>3</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9488,37 +9486,39 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9552,11 +9552,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9619,30 +9619,30 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9732,82 +9732,739 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-PT</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada preto</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>4851133050</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O136"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,9 +592,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,16 +662,18 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,37 +682,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +750,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -819,9 +823,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -830,11 +834,11 @@
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +885,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -889,47 +893,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +971,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1044,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,55 +1108,59 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,7 +1194,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1216,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1267,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1282,19 +1294,19 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1331,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1355,19 +1367,19 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1428,19 +1440,19 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1470,20 +1482,20 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1491,7 +1503,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1501,19 +1513,19 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,7 +1550,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1547,24 +1559,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1574,19 +1586,19 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1647,19 +1659,19 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,12 +1696,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
@@ -1697,20 +1709,20 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1720,19 +1732,19 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,17 +1772,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1793,19 +1805,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1843,7 +1855,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1866,19 +1878,19 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1915,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1988,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,24 +1997,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2058,11 +2070,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2134,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,17 +2210,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2250,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2353,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2396,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,7 +2426,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2423,24 +2435,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2508,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2572,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,7 +2581,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2578,15 +2590,15 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2615,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,17 +2648,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2715,11 +2727,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2761,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2822,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,12 +2864,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
@@ -2865,20 +2877,20 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2936,9 +2948,9 @@
       <c r="I34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3009,9 +3021,9 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,7 +3083,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3080,24 +3092,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,7 +3156,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3152,10 +3164,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3164,39 +3174,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3230,7 +3238,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3264,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3297,17 +3305,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3378,9 +3386,9 @@
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3410,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3451,9 +3459,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3483,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3513,7 +3521,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3522,24 +3530,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3556,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3595,11 +3603,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3662,17 +3670,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3702,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3741,11 +3749,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3775,12 +3783,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3805,7 +3813,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3813,47 +3821,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3878,33 +3890,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3921,12 +3933,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3964,7 +3976,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3994,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4033,11 +4045,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4067,12 +4079,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4097,33 +4109,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4133,19 +4145,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4173,17 +4185,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4206,19 +4218,19 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4252,11 +4264,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4279,19 +4291,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4316,20 +4328,20 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4338,11 +4350,11 @@
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4352,19 +4364,19 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4389,33 +4401,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4425,19 +4437,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4471,11 +4483,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4498,19 +4510,19 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4535,33 +4547,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4571,19 +4583,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4608,7 +4620,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4621,20 +4633,20 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4644,19 +4656,19 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4690,11 +4702,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4717,19 +4729,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4754,33 +4766,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4797,12 +4809,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4830,17 +4842,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4870,12 +4882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4900,7 +4912,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4908,10 +4920,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4920,39 +4930,37 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4977,7 +4985,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4986,24 +4994,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5020,12 +5028,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5050,12 +5058,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
@@ -5063,20 +5071,20 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5093,12 +5101,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5123,7 +5131,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5131,51 +5139,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5209,7 +5213,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5243,12 +5247,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5273,7 +5277,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5282,24 +5286,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5316,12 +5320,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5346,7 +5350,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5354,10 +5358,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5366,39 +5368,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5431,51 +5431,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5503,9 +5499,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
@@ -5543,12 +5539,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5620,12 +5616,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5659,7 +5655,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5693,12 +5689,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5723,7 +5719,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5736,20 +5732,20 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5766,12 +5762,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5843,12 +5839,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5876,9 +5872,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
@@ -5916,12 +5912,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5955,11 +5951,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5989,12 +5985,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6019,7 +6015,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6027,8 +6023,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6037,37 +6035,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6100,47 +6100,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6168,17 +6172,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6208,12 +6212,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6238,7 +6242,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6246,47 +6250,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6320,7 +6328,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6354,12 +6362,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6384,7 +6392,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6393,24 +6401,24 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6427,12 +6435,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6457,7 +6465,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6465,8 +6473,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>1</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6475,37 +6485,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6533,9 +6545,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -6573,12 +6585,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6612,7 +6624,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6646,12 +6658,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6707,7 +6719,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6719,12 +6731,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6749,7 +6761,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6771,11 +6783,11 @@
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6792,12 +6804,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6865,12 +6877,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6938,12 +6950,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6971,17 +6983,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7011,12 +7023,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7050,11 +7062,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7084,12 +7096,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7125,9 +7137,9 @@
       <c r="I91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7157,12 +7169,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7187,33 +7199,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7230,12 +7242,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7269,11 +7281,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7303,12 +7315,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7342,11 +7354,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7376,12 +7388,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7406,7 +7418,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7415,24 +7427,24 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7449,12 +7461,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7482,17 +7494,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7522,12 +7534,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7561,11 +7573,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7595,12 +7607,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7634,11 +7646,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7668,12 +7680,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7698,33 +7710,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7741,12 +7753,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7784,7 +7796,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7814,12 +7826,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7844,29 +7856,29 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
+          <t>R$ 60,00</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,8%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,9%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -7887,12 +7899,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7917,7 +7929,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7926,24 +7938,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7960,12 +7972,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7999,11 +8011,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8033,12 +8045,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8063,33 +8075,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 269,00</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,7%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8106,12 +8118,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8145,11 +8157,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8179,12 +8191,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8218,11 +8230,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8252,12 +8264,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8282,33 +8294,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8325,12 +8337,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8358,22 +8370,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>3</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
@@ -8381,7 +8393,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8398,12 +8410,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8437,11 +8449,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8471,12 +8483,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8501,33 +8513,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 209,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,8%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5000,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8544,12 +8556,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8574,7 +8586,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8583,24 +8595,24 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8617,12 +8629,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8647,7 +8659,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8655,51 +8667,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8724,33 +8732,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 269,00</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,7%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>27</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8767,12 +8775,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8800,17 +8808,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8840,12 +8848,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8870,7 +8878,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8878,10 +8886,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -8890,39 +8896,37 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8947,33 +8951,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8990,12 +8994,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9020,33 +9024,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9063,12 +9067,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9093,7 +9097,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9101,10 +9105,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9113,39 +9115,37 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 209,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9179,24 +9179,24 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>51</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5000,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9251,51 +9251,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I120" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9320,7 +9316,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9328,8 +9324,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9338,37 +9336,39 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9396,17 +9396,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9436,12 +9436,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9474,51 +9474,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I123" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9543,7 +9539,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9551,47 +9547,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9616,33 +9616,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9698,7 +9698,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9732,12 +9732,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9770,8 +9770,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="n">
-        <v>1</v>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9780,37 +9782,39 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9835,33 +9839,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9878,12 +9882,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9908,55 +9912,59 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9992,9 +10000,9 @@
       <c r="I130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10024,12 +10032,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10054,33 +10062,33 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10097,12 +10105,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10127,7 +10135,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10135,8 +10143,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I132" s="2" t="n">
-        <v>3</v>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10145,37 +10155,39 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10209,11 +10221,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10243,12 +10255,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10276,30 +10288,30 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10316,12 +10328,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10389,82 +10401,739 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-PT</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada preto</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>4851133050</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O136" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O136"/>
+  <autoFilter ref="A1:O145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$148</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O145"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,41 +680,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -750,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -821,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -855,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -932,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -971,11 +967,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1005,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1046,9 +1042,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1155,14 +1151,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1194,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1228,14 +1224,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1261,17 +1257,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1301,14 +1297,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1331,16 +1327,18 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1349,39 +1347,41 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1447,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1477,20 +1477,20 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1499,11 +1499,11 @@
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1550,20 +1550,20 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1572,11 +1572,11 @@
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1634,9 +1634,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1666,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1705,24 +1705,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1739,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1769,33 +1769,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1851,11 +1851,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1918,17 +1918,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1951,21 +1951,21 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -1988,33 +1988,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2024,21 +2024,21 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2134,33 +2134,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2177,14 +2177,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2220,20 +2220,20 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,14 +2250,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2291,9 +2291,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2396,14 +2396,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2469,14 +2469,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2508,11 +2508,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2542,14 +2542,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2615,14 +2615,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2656,9 +2656,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2688,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2761,14 +2761,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2809,15 +2809,15 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2834,14 +2834,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -2867,17 +2867,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2948,9 +2948,9 @@
       <c r="I34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3053,14 +3053,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3083,33 +3083,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3126,14 +3126,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3165,11 +3165,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3272,14 +3272,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3302,33 +3302,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3345,14 +3345,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3384,11 +3384,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3491,14 +3491,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3521,33 +3521,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3564,14 +3564,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3603,11 +3603,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,14 +3637,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3678,9 +3678,9 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3710,14 +3710,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -3758,15 +3758,15 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3783,14 +3783,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3821,10 +3821,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3833,41 +3831,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3899,11 +3895,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3933,14 +3929,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -3972,11 +3968,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4006,14 +4002,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4036,7 +4032,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4044,8 +4040,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4054,39 +4052,41 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4152,14 +4152,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4191,11 +4191,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4225,14 +4225,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4266,9 +4266,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4298,14 +4298,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4331,17 +4331,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4412,9 +4412,9 @@
       <c r="I54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4444,14 +4444,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4483,11 +4483,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4517,14 +4517,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4547,33 +4547,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4590,14 +4590,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4629,11 +4629,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4663,14 +4663,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4702,11 +4702,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4736,14 +4736,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4766,20 +4766,20 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4788,11 +4788,11 @@
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4802,21 +4802,21 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4842,17 +4842,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4875,21 +4875,21 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4921,11 +4921,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4948,21 +4948,21 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -4990,20 +4990,20 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5028,14 +5028,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5058,33 +5058,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5101,14 +5101,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5140,11 +5140,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5174,14 +5174,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5213,24 +5213,24 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5247,14 +5247,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5282,20 +5282,20 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5320,14 +5320,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5359,11 +5359,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5393,14 +5393,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5432,11 +5432,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5466,14 +5466,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5505,24 +5505,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5539,14 +5539,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5577,10 +5577,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5589,41 +5587,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5655,11 +5651,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5689,14 +5685,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5728,11 +5724,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5762,12 +5758,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5839,14 +5835,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5878,7 +5874,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5912,14 +5908,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -5951,11 +5947,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5985,12 +5981,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6062,14 +6058,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6092,7 +6088,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6100,10 +6096,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6112,41 +6106,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6172,17 +6164,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6212,12 +6204,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6289,14 +6281,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6319,7 +6311,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6327,8 +6319,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6337,39 +6331,41 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6392,33 +6388,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6435,12 +6431,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6512,14 +6508,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6545,9 +6541,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -6585,14 +6581,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6615,7 +6611,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6624,24 +6620,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6658,14 +6654,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6688,7 +6684,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6696,8 +6692,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6706,39 +6704,41 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6761,20 +6761,20 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6783,11 +6783,11 @@
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6804,14 +6804,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6843,11 +6843,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6877,14 +6877,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6918,9 +6918,9 @@
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -6950,14 +6950,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6989,24 +6989,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7023,14 +7023,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7062,11 +7062,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7096,14 +7096,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7135,11 +7135,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7169,14 +7169,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7242,14 +7242,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7315,14 +7315,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7388,14 +7388,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7429,9 +7429,9 @@
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7461,14 +7461,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7502,9 +7502,9 @@
       <c r="I96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7534,14 +7534,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7575,9 +7575,9 @@
       <c r="I97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7607,14 +7607,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7640,17 +7640,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7680,14 +7680,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7719,11 +7719,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7753,14 +7753,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7792,11 +7792,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7826,14 +7826,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7856,33 +7856,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7899,14 +7899,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -7938,11 +7938,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7972,14 +7972,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8011,11 +8011,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8045,14 +8045,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8075,33 +8075,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 60,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8118,14 +8118,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8151,17 +8151,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8191,14 +8191,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8230,11 +8230,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8264,14 +8264,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8294,33 +8294,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8337,14 +8337,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8367,33 +8367,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8410,14 +8410,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8449,11 +8449,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8483,14 +8483,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8513,33 +8513,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>▼ 88,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8556,14 +8556,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8591,20 +8591,20 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8629,14 +8629,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8668,11 +8668,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8702,14 +8702,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8732,20 +8732,20 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 269,00</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,7%</t>
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,8%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8754,11 +8754,11 @@
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8775,14 +8775,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8805,33 +8805,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8921,14 +8921,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -8951,33 +8951,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
+          <t>R$ 269,00</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,7%</t>
+          <t>▲ 21,7%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,6%</t>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8994,14 +8994,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9024,33 +9024,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>▼ 55,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>5</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9067,14 +9067,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -9140,14 +9140,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9170,33 +9170,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 209,00</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5000,0%</t>
+        <v>42</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9213,14 +9213,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9243,33 +9243,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 250,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9286,14 +9286,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9324,10 +9324,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9336,41 +9334,39 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9393,7 +9389,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 209,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9402,24 +9398,24 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>51</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5000,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9436,14 +9432,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9466,7 +9462,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9475,24 +9471,24 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9509,12 +9505,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9586,14 +9582,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9625,11 +9621,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9659,14 +9655,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9698,11 +9694,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9732,12 +9728,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9809,14 +9805,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9848,11 +9844,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9882,14 +9878,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9912,7 +9908,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9920,10 +9916,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -9932,41 +9926,39 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -9989,7 +9981,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -9997,8 +9989,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I130" s="2" t="n">
-        <v>0</v>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10007,39 +10001,41 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10065,17 +10061,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10105,12 +10101,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10182,14 +10178,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10223,9 +10219,9 @@
       <c r="I133" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10255,14 +10251,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10285,33 +10281,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10328,14 +10324,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10358,7 +10354,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10366,8 +10362,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="n">
-        <v>0</v>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10376,39 +10374,41 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10440,11 +10440,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
@@ -10474,14 +10474,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10504,25 +10504,25 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10547,14 +10547,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10580,17 +10580,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10620,14 +10620,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10659,11 +10659,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
@@ -10693,14 +10693,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10726,17 +10726,17 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10766,14 +10766,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10796,33 +10796,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10839,14 +10839,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10878,11 +10878,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10912,14 +10912,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -10942,33 +10942,33 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10985,14 +10985,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-095-PT</t>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11033,15 +11033,15 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11058,82 +11058,301 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-PT</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada preto</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>4851133050</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O145" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O145"/>
+  <autoFilter ref="A1:O148"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
+++ b/saida_skus/SKU_UTD-095-PT-SECA-SALADA-PRETO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -826,15 +826,15 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -889,51 +889,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -967,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1001,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1042,9 +1038,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1104,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1112,10 +1108,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1124,39 +1118,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1190,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1263,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1297,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1374,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1413,11 +1405,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1447,12 +1439,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1480,13 +1472,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1520,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1550,16 +1542,18 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1568,37 +1562,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1632,11 +1628,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1666,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1696,7 +1692,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1718,11 +1714,11 @@
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1739,12 +1735,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1769,7 +1765,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1777,47 +1773,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1851,11 +1851,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1918,9 +1918,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -1958,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2104,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2134,33 +2134,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2170,19 +2170,19 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2243,19 +2243,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2291,9 +2291,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2316,19 +2316,19 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
@@ -2366,20 +2366,20 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2389,19 +2389,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2429,17 +2429,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2462,19 +2462,19 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2508,11 +2508,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2535,19 +2535,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2572,33 +2572,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2654,24 +2654,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2688,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2873,11 +2873,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2946,11 +2946,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3010,33 +3010,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3167,9 +3167,9 @@
       <c r="I37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3247,15 +3247,15 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3311,24 +3311,24 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3345,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3384,11 +3384,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3530,11 +3530,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3603,11 +3603,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3749,16 +3749,16 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3783,12 +3783,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3856,12 +3856,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3897,9 +3897,9 @@
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3962,17 +3962,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4040,51 +4040,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4118,7 +4114,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4152,12 +4148,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4182,7 +4178,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4191,24 +4187,24 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4225,12 +4221,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4264,7 +4260,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4298,12 +4294,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4371,12 +4367,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4410,11 +4406,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4444,12 +4440,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4474,7 +4470,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4482,47 +4478,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4550,17 +4550,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4590,12 +4590,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4629,11 +4629,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4702,11 +4702,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4766,33 +4766,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4848,11 +4848,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4882,12 +4882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4921,11 +4921,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4985,33 +4985,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5021,19 +5021,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5061,17 +5061,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5094,19 +5094,19 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5140,11 +5140,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5167,19 +5167,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5204,33 +5204,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5240,19 +5240,19 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5277,33 +5277,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5313,19 +5313,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5359,11 +5359,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5386,19 +5386,19 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -5441,15 +5441,15 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5496,33 +5496,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5664,11 +5664,11 @@
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5685,12 +5685,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5715,33 +5715,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5796,51 +5796,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5908,12 +5904,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5938,7 +5934,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5947,24 +5943,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5981,12 +5977,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6011,7 +6007,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6019,10 +6015,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I76" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6031,39 +6025,37 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6099,9 +6091,9 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6131,12 +6123,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6172,9 +6164,9 @@
       <c r="I78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6204,12 +6196,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6281,12 +6273,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6311,7 +6303,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6319,10 +6311,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6331,39 +6321,37 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6391,17 +6379,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6431,12 +6419,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6508,12 +6496,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6581,12 +6569,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6611,7 +6599,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6620,24 +6608,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6654,12 +6642,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6731,12 +6719,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6761,16 +6749,18 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6779,37 +6769,39 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6837,17 +6829,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6877,12 +6869,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6907,7 +6899,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6915,8 +6907,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -6925,37 +6919,39 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6980,7 +6976,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6991,9 +6987,9 @@
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7002,11 +6998,11 @@
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7023,12 +7019,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7053,7 +7049,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7062,24 +7058,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7096,12 +7092,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7126,7 +7122,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7134,47 +7130,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7202,13 +7202,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7242,12 +7242,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7429,9 +7429,9 @@
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7440,11 +7440,11 @@
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7502,9 +7502,9 @@
       <c r="I96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7575,9 +7575,9 @@
       <c r="I97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7680,12 +7680,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7719,11 +7719,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7792,11 +7792,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7899,12 +7899,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7938,11 +7938,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8011,11 +8011,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8075,33 +8075,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8157,11 +8157,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8230,11 +8230,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8264,12 +8264,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8294,33 +8294,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8370,17 +8370,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8410,12 +8410,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8449,11 +8449,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8513,33 +8513,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 60,00</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>200,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8586,33 +8586,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8668,11 +8668,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8702,12 +8702,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8732,33 +8732,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,8%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 88,9%</t>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
@@ -8818,20 +8818,20 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8887,11 +8887,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8951,33 +8951,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 269,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9024,33 +9024,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9067,12 +9067,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9106,11 +9106,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9140,12 +9140,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9170,33 +9170,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 221,00</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,7%</t>
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 88,8%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,6%</t>
+          <t>▼ 88,9%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9246,9 +9246,9 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 55,6%</t>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9286,12 +9286,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9325,11 +9325,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9389,33 +9389,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 209,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 269,00</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,7%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5000,0%</t>
+        <v>27</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9432,12 +9432,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9462,33 +9462,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>▲ 250,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9543,10 +9543,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9555,39 +9553,37 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9612,33 +9608,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 221,00</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,7%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>42</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,6%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9655,12 +9651,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9685,12 +9681,12 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 55,6%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
@@ -9698,20 +9694,20 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9728,12 +9724,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9758,7 +9754,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9766,10 +9762,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9778,39 +9772,37 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9835,7 +9827,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 209,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -9844,24 +9836,24 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>51</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5000,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9878,12 +9870,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9908,7 +9900,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9917,24 +9909,24 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>▲ 250,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9951,12 +9943,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10028,12 +10020,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10067,11 +10059,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10101,12 +10093,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10131,7 +10123,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10139,51 +10131,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I132" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10208,7 +10196,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10216,8 +10204,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="n">
-        <v>0</v>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10226,37 +10216,39 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10284,17 +10276,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10324,12 +10316,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10354,7 +10346,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10362,10 +10354,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10374,39 +10364,37 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10431,7 +10419,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10439,47 +10427,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10504,33 +10496,33 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10547,12 +10539,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10577,7 +10569,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10585,8 +10577,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="2" t="n">
-        <v>0</v>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10595,37 +10589,39 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10659,7 +10655,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10681,7 +10677,7 @@
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
@@ -10693,12 +10689,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10723,33 +10719,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10766,12 +10762,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10796,55 +10792,59 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10912,12 +10912,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10942,25 +10942,25 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11033,15 +11033,15 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11058,12 +11058,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
@@ -11131,12 +11131,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11161,33 +11161,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>200,0%</t>
-        </is>
-      </c>
-      <c r="L146" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11237,17 +11237,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11277,82 +11277,520 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4851133050</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-PT</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada preto</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>4904644460</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4502732547</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-PT</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada preto</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>4851133050</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O148" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O148"/>
+  <autoFilter ref="A1:O154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>